--- a/SAP Reports/Input Files/Bal-Sht Jan 26/BS CHALLMC JAN 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/Bal-Sht Jan 26/BS CHALLMC JAN 26 ANNUAL.xlsx
@@ -14,51 +14,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="134">
   <si>
     <t>Account Name</t>
   </si>
   <si>
-    <t>Current Period</t>
-  </si>
-  <si>
-    <t>Comparison Period</t>
-  </si>
-  <si>
-    <t>Difference Amount</t>
-  </si>
-  <si>
-    <t>Percentage Difference</t>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>System Currency</t>
   </si>
   <si>
     <t>Assets</t>
   </si>
   <si>
-    <t>$  4,366,527.98</t>
-  </si>
-  <si>
-    <t>$  5,069,091.89</t>
-  </si>
-  <si>
-    <t>$ -702,563.91</t>
-  </si>
-  <si>
-    <t>% -13.860</t>
+    <t>$  4,336,792.49</t>
   </si>
   <si>
     <t>Current Assets - Cash and Equiv</t>
   </si>
   <si>
-    <t>$  4,225,319.58</t>
-  </si>
-  <si>
-    <t>$  4,940,527.94</t>
-  </si>
-  <si>
-    <t>$ -715,208.36</t>
-  </si>
-  <si>
-    <t>% -14.476</t>
+    <t>$  4,195,584.09</t>
   </si>
   <si>
     <t>Cash and Equiv - CASH AND EQUITY</t>
@@ -67,42 +43,18 @@
     <t>$  2,807,772.22</t>
   </si>
   <si>
-    <t>$  2,146,549.01</t>
-  </si>
-  <si>
-    <t>$ 661,223.21</t>
-  </si>
-  <si>
-    <t>% 30.804</t>
-  </si>
-  <si>
     <t>110101-02-000-00 - SSB-CHECKING ACCT</t>
   </si>
   <si>
     <t>$  770,005.78</t>
   </si>
   <si>
-    <t>$  1,439,593.84</t>
-  </si>
-  <si>
-    <t>$ -669,588.06</t>
-  </si>
-  <si>
-    <t>% -46.512</t>
-  </si>
-  <si>
     <t>110250-02-000-00 - ELAN CREDIT CARD</t>
   </si>
   <si>
     <t>$  18,811.16</t>
   </si>
   <si>
-    <t>$ 18,811.16</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
     <t>110400-02-000-00 - SSB HIGH YIELD MMKT</t>
   </si>
   <si>
@@ -115,24 +67,12 @@
     <t>$  2,000,000.00</t>
   </si>
   <si>
-    <t>$  700,000.00</t>
-  </si>
-  <si>
-    <t>$ 1,300,000.00</t>
-  </si>
-  <si>
-    <t>% 185.714</t>
-  </si>
-  <si>
     <t>110705-02-000-00 - CHECKING CLEARING ACCOUNT</t>
   </si>
   <si>
     <t>$  12,000.11</t>
   </si>
   <si>
-    <t>$ 12,000.11</t>
-  </si>
-  <si>
     <t>__________________</t>
   </si>
   <si>
@@ -145,31 +85,13 @@
     <t>Receivables - RECEIVABLES</t>
   </si>
   <si>
-    <t>$  1,410,771.54</t>
-  </si>
-  <si>
-    <t>$  2,788,378.93</t>
-  </si>
-  <si>
-    <t>$ -1,377,607.39</t>
-  </si>
-  <si>
-    <t>% -49.405</t>
+    <t>$  1,381,036.05</t>
   </si>
   <si>
     <t>120000-02-000-00 - ACCOUNTS RECEIVABLE</t>
   </si>
   <si>
-    <t>$  3,642,004.00</t>
-  </si>
-  <si>
-    <t>$  3,820,111.39</t>
-  </si>
-  <si>
-    <t>$ -178,107.39</t>
-  </si>
-  <si>
-    <t>% -4.662</t>
+    <t>$  3,612,268.51</t>
   </si>
   <si>
     <t>120015-02-000-00 - LOAN TO/FROM TGI</t>
@@ -184,30 +106,12 @@
     <t>$ (2,400,000.00)</t>
   </si>
   <si>
-    <t>$ (1,200,000.00)</t>
-  </si>
-  <si>
-    <t>$ -1,200,000.00</t>
-  </si>
-  <si>
-    <t>% -100.000</t>
-  </si>
-  <si>
     <t>120060-02-000-00 - LOAN TO EMPLOYEE</t>
   </si>
   <si>
     <t>$  18,767.54</t>
   </si>
   <si>
-    <t>$  18,267.54</t>
-  </si>
-  <si>
-    <t>$ 500.00</t>
-  </si>
-  <si>
-    <t>% 2.737</t>
-  </si>
-  <si>
     <t>Total Receivables - RECEIVABLES</t>
   </si>
   <si>
@@ -217,18 +121,12 @@
     <t>$  6,775.82</t>
   </si>
   <si>
+    <t>120452-02-000-00 - SECURITY DEPOSIT (PEPCO &amp; GAS)</t>
+  </si>
+  <si>
     <t>$  5,600.00</t>
   </si>
   <si>
-    <t>$ 1,175.82</t>
-  </si>
-  <si>
-    <t>% 20.997</t>
-  </si>
-  <si>
-    <t>120452-02-000-00 - SECURITY DEPOSIT (PEPCO &amp; GAS)</t>
-  </si>
-  <si>
     <t>121810-02-000-00 - DUE TO PAYCHEX</t>
   </si>
   <si>
@@ -247,27 +145,12 @@
     <t>$  18,357.40</t>
   </si>
   <si>
-    <t>$  5,712.95</t>
-  </si>
-  <si>
-    <t>$ 12,644.45</t>
-  </si>
-  <si>
-    <t>% 221.330</t>
-  </si>
-  <si>
     <t>FixedAssets - FIXED ASSETS</t>
   </si>
   <si>
     <t>$  1,734,140.75</t>
   </si>
   <si>
-    <t>$  1,721,496.30</t>
-  </si>
-  <si>
-    <t>% 0.735</t>
-  </si>
-  <si>
     <t>120470-02-000-00 - COMPUTER/OFFICE MACHINES</t>
   </si>
   <si>
@@ -292,30 +175,12 @@
     <t>$  690,348.30</t>
   </si>
   <si>
-    <t>$  686,703.85</t>
-  </si>
-  <si>
-    <t>$ 3,644.45</t>
-  </si>
-  <si>
-    <t>% 0.531</t>
-  </si>
-  <si>
     <t>120650-02-000-00 - HVAC</t>
   </si>
   <si>
     <t>$  208,256.56</t>
   </si>
   <si>
-    <t>$  199,256.56</t>
-  </si>
-  <si>
-    <t>$ 9,000.00</t>
-  </si>
-  <si>
-    <t>% 4.517</t>
-  </si>
-  <si>
     <t>120700-02-000-00 - VEHICLES &amp; HEAV EQUIP</t>
   </si>
   <si>
@@ -415,15 +280,6 @@
     <t>$  268,413.61</t>
   </si>
   <si>
-    <t>$  869,039.34</t>
-  </si>
-  <si>
-    <t>$ -600,625.73</t>
-  </si>
-  <si>
-    <t>% -69.114</t>
-  </si>
-  <si>
     <t>Current Liabs - CURRENT LIABILITIES</t>
   </si>
   <si>
@@ -439,45 +295,18 @@
     <t>$  260,643.00</t>
   </si>
   <si>
-    <t>$  864,656.20</t>
-  </si>
-  <si>
-    <t>$ -604,013.20</t>
-  </si>
-  <si>
-    <t>% -69.856</t>
-  </si>
-  <si>
-    <t>220256-02-000-00 - WAGES PAYABLES</t>
+    <t>220256-02-000-00 - WAGES PAYABLE</t>
   </si>
   <si>
     <t>$  247,600.32</t>
   </si>
   <si>
-    <t>$  863,283.00</t>
-  </si>
-  <si>
-    <t>$ -615,682.68</t>
-  </si>
-  <si>
-    <t>% -71.319</t>
-  </si>
-  <si>
     <t>250900-02-000-00 - 401 K LIABILITY -PAYABLE</t>
   </si>
   <si>
     <t>$  13,042.68</t>
   </si>
   <si>
-    <t>$  1,373.20</t>
-  </si>
-  <si>
-    <t>$ 11,669.48</t>
-  </si>
-  <si>
-    <t>% 849.802</t>
-  </si>
-  <si>
     <t>Total Payroll Liabs - PAYROLL LIABILITIES</t>
   </si>
   <si>
@@ -487,36 +316,18 @@
     <t>$  7,770.61</t>
   </si>
   <si>
-    <t>$  4,383.14</t>
-  </si>
-  <si>
-    <t>$ 3,387.47</t>
-  </si>
-  <si>
-    <t>% 77.284</t>
-  </si>
-  <si>
     <t>220260-02-000-00 - AFLAC PAYABLES</t>
   </si>
   <si>
     <t>$  6,959.70</t>
   </si>
   <si>
-    <t>$ 2,576.56</t>
-  </si>
-  <si>
-    <t>% 58.783</t>
-  </si>
-  <si>
     <t>250920-02-000-00 - HUMANA INS(VISION &amp; DENTAL)</t>
   </si>
   <si>
     <t>$  810.91</t>
   </si>
   <si>
-    <t>$ 810.91</t>
-  </si>
-  <si>
     <t>Total OtherLiability - OTHER LIBILITY</t>
   </si>
   <si>
@@ -541,31 +352,13 @@
     <t>Equity</t>
   </si>
   <si>
-    <t>$  4,098,114.37</t>
-  </si>
-  <si>
-    <t>$  4,200,052.55</t>
-  </si>
-  <si>
-    <t>$ -101,938.18</t>
-  </si>
-  <si>
-    <t>% -2.427</t>
+    <t>$  4,068,378.88</t>
   </si>
   <si>
     <t>Stock Equity - STOCK HOLDERS EQUITY</t>
   </si>
   <si>
-    <t>$  3,761,458.56</t>
-  </si>
-  <si>
-    <t>$  3,595,458.56</t>
-  </si>
-  <si>
-    <t>$ 166,000.00</t>
-  </si>
-  <si>
-    <t>% 4.617</t>
+    <t>$  4,355,552.20</t>
   </si>
   <si>
     <t>Common Stock - COMMON STOCK</t>
@@ -595,19 +388,13 @@
     <t>Surplus - SURPLUS</t>
   </si>
   <si>
-    <t>$  3,342,245.56</t>
-  </si>
-  <si>
-    <t>$  3,176,245.56</t>
-  </si>
-  <si>
-    <t>% 5.226</t>
+    <t>$  3,936,339.20</t>
   </si>
   <si>
     <t>368400-02-000-00 - RETAINED EARNINGS</t>
   </si>
   <si>
-    <t>$  7,736,497.56</t>
+    <t>$  8,330,591.20</t>
   </si>
   <si>
     <t>368350-02-000-00 - PROFIT DISTRIBUTION</t>
@@ -616,12 +403,6 @@
     <t>$ (4,394,252.00)</t>
   </si>
   <si>
-    <t>$ (4,560,252.00)</t>
-  </si>
-  <si>
-    <t>% 3.640</t>
-  </si>
-  <si>
     <t>Total Surplus - SURPLUS</t>
   </si>
   <si>
@@ -631,16 +412,7 @@
     <t>Profit Period</t>
   </si>
   <si>
-    <t>$  336,655.81</t>
-  </si>
-  <si>
-    <t>$  604,593.99</t>
-  </si>
-  <si>
-    <t>$ -267,938.18</t>
-  </si>
-  <si>
-    <t>% -44.317</t>
+    <t>$ (287,173.32)</t>
   </si>
   <si>
     <t>Total Equity</t>
@@ -1501,1498 +1273,1228 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
 		</row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
 		</row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
 		</row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
 		</row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
 		</row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
 		</row>
     <row r="27">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
 		</row>
     <row r="29">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
 		</row>
     <row r="35">
       <c r="B35" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
 		</row>
     <row r="39">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
 		</row>
     <row r="41">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
 		</row>
     <row r="43">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
 		</row>
     <row r="55">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56">
 		</row>
     <row r="57">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
 		</row>
     <row r="69">
       <c r="B69" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
-      </c>
-      <c r="D70" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
 		</row>
     <row r="73">
       <c r="A73" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C74" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79">
 		</row>
     <row r="80">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
-      </c>
-      <c r="D80" t="s">
-        <v>134</v>
-      </c>
-      <c r="E80" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81">
 		</row>
     <row r="82">
       <c r="A82" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" t="s">
-        <v>134</v>
-      </c>
-      <c r="E82" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83">
 		</row>
     <row r="84">
       <c r="A84" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85">
 		</row>
     <row r="86">
       <c r="B86" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89">
 		</row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>141</v>
-      </c>
-      <c r="D90" t="s">
-        <v>142</v>
-      </c>
-      <c r="E90" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91">
 		</row>
     <row r="92">
       <c r="A92" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
-      </c>
-      <c r="D92" t="s">
-        <v>147</v>
-      </c>
-      <c r="E92" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="C93" t="s">
-        <v>151</v>
-      </c>
-      <c r="D93" t="s">
-        <v>152</v>
-      </c>
-      <c r="E93" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
-      </c>
-      <c r="D95" t="s">
-        <v>142</v>
-      </c>
-      <c r="E95" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97">
 		</row>
     <row r="98">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="C98" t="s">
-        <v>157</v>
-      </c>
-      <c r="D98" t="s">
-        <v>158</v>
-      </c>
-      <c r="E98" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99">
 		</row>
     <row r="100">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
-      </c>
-      <c r="D100" t="s">
-        <v>162</v>
-      </c>
-      <c r="E100" t="s">
-        <v>163</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>165</v>
-      </c>
-      <c r="D101" t="s">
-        <v>166</v>
-      </c>
-      <c r="E101" t="s">
-        <v>28</v>
+        <v>103</v>
+      </c>
+      <c r="C101" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D103" t="s">
-        <v>158</v>
-      </c>
-      <c r="E103" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
 		</row>
     <row r="106">
       <c r="B106" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C106" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
-      </c>
-      <c r="D107" t="s">
-        <v>134</v>
-      </c>
-      <c r="E107" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C108" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
 		</row>
     <row r="110">
       <c r="A110" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111">
 		</row>
     <row r="112">
       <c r="A112" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113">
 		</row>
     <row r="114">
       <c r="B114" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C114" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C117" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C119" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C120" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>133</v>
-      </c>
-      <c r="D121" t="s">
-        <v>134</v>
-      </c>
-      <c r="E121" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="B122" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="C122" t="s">
-        <v>176</v>
-      </c>
-      <c r="D122" t="s">
-        <v>177</v>
-      </c>
-      <c r="E122" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123">
 		</row>
     <row r="124">
       <c r="A124" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="B124" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="C124" t="s">
-        <v>181</v>
-      </c>
-      <c r="D124" t="s">
-        <v>182</v>
-      </c>
-      <c r="E124" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125">
 		</row>
     <row r="126">
       <c r="A126" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="B126" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="C126" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127">
 		</row>
     <row r="128">
       <c r="A128" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="B128" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="C128" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C129" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>187</v>
+        <v>118</v>
       </c>
       <c r="B130" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C131" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132">
 		</row>
     <row r="133">
       <c r="A133" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="B133" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="C133" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134">
 		</row>
     <row r="135">
       <c r="A135" t="s">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="B135" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="C135" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C136" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="B137" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139">
 		</row>
     <row r="140">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B140" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="C140" t="s">
-        <v>194</v>
-      </c>
-      <c r="D140" t="s">
-        <v>182</v>
-      </c>
-      <c r="E140" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
     </row>
     <row r="141">
 		</row>
     <row r="142">
       <c r="A142" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="B142" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="C142" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="B143" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="C143" t="s">
-        <v>200</v>
-      </c>
-      <c r="D143" t="s">
-        <v>182</v>
-      </c>
-      <c r="E143" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C144" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="B145" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="C145" t="s">
-        <v>194</v>
-      </c>
-      <c r="D145" t="s">
-        <v>182</v>
-      </c>
-      <c r="E145" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C146" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C147" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="B148" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="C148" t="s">
-        <v>181</v>
-      </c>
-      <c r="D148" t="s">
-        <v>182</v>
-      </c>
-      <c r="E148" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C149" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="B150" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
-      </c>
-      <c r="D150" t="s">
-        <v>207</v>
-      </c>
-      <c r="E150" t="s">
-        <v>208</v>
+        <v>132</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C151" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="C152" t="s">
-        <v>176</v>
-      </c>
-      <c r="D152" t="s">
-        <v>177</v>
-      </c>
-      <c r="E152" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="C155" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156">
